--- a/database.xlsx
+++ b/database.xlsx
@@ -397,126 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>en</v>
-      </c>
-      <c r="B1" t="str">
-        <v>vi</v>
-      </c>
-      <c r="C1" t="str">
-        <v>pron</v>
-      </c>
-      <c r="D1" t="str">
-        <v>pos</v>
-      </c>
-      <c r="E1" t="str">
-        <v>category</v>
-      </c>
-      <c r="F1" t="str">
-        <v>id</v>
-      </c>
-      <c r="G1" t="str">
-        <v>isHard</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Quả táo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>/ˈæpl/</v>
-      </c>
-      <c r="D2" t="str">
-        <v>n</v>
-      </c>
-      <c r="E2" t="str">
-        <v>test1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Beautiful</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Xinh đẹp</v>
-      </c>
-      <c r="C3" t="str">
-        <v>/ˈbjuːtɪfl/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>adj</v>
-      </c>
-      <c r="E3" t="str">
-        <v>test1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Run</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Chạy</v>
-      </c>
-      <c r="C4" t="str">
-        <v>/rʌn/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>v</v>
-      </c>
-      <c r="E4" t="str">
-        <v>test1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>HI</v>
-      </c>
-      <c r="B5" t="str">
-        <v>xin chào</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>test1</v>
-      </c>
-      <c r="F5">
-        <v>1773633454411</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -397,10 +397,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>en</v>
+      </c>
+      <c r="B1" t="str">
+        <v>vi</v>
+      </c>
+      <c r="C1" t="str">
+        <v>pron</v>
+      </c>
+      <c r="D1" t="str">
+        <v>pos</v>
+      </c>
+      <c r="E1" t="str">
+        <v>category</v>
+      </c>
+      <c r="F1" t="str">
+        <v>id</v>
+      </c>
+      <c r="G1" t="str">
+        <v>isHard</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Quả táo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>/ˈæpl/</v>
+      </c>
+      <c r="D2" t="str">
+        <v>n</v>
+      </c>
+      <c r="E2" t="str">
+        <v>t1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Beautiful</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Xinh đẹp</v>
+      </c>
+      <c r="C3" t="str">
+        <v>/ˈbjuːtɪfl/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>adj</v>
+      </c>
+      <c r="E3" t="str">
+        <v>t1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Run</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Chạy</v>
+      </c>
+      <c r="C4" t="str">
+        <v>/rʌn/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>v</v>
+      </c>
+      <c r="E4" t="str">
+        <v>t1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -491,9 +491,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Hello</v>
+      </c>
+      <c r="B5" t="str">
+        <v>xin chào</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>t1</v>
+      </c>
+      <c r="F5">
+        <v>1773639230959</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>english</v>
+      </c>
+      <c r="B6" t="str">
+        <v>tiếng anh</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>t1</v>
+      </c>
+      <c r="F6">
+        <v>1773640370257</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -397,149 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>en</v>
-      </c>
-      <c r="B1" t="str">
-        <v>vi</v>
-      </c>
-      <c r="C1" t="str">
-        <v>pron</v>
-      </c>
-      <c r="D1" t="str">
-        <v>pos</v>
-      </c>
-      <c r="E1" t="str">
-        <v>category</v>
-      </c>
-      <c r="F1" t="str">
-        <v>id</v>
-      </c>
-      <c r="G1" t="str">
-        <v>isHard</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Quả táo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>/ˈæpl/</v>
-      </c>
-      <c r="D2" t="str">
-        <v>n</v>
-      </c>
-      <c r="E2" t="str">
-        <v>t1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Beautiful</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Xinh đẹp</v>
-      </c>
-      <c r="C3" t="str">
-        <v>/ˈbjuːtɪfl/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>adj</v>
-      </c>
-      <c r="E3" t="str">
-        <v>t1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Run</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Chạy</v>
-      </c>
-      <c r="C4" t="str">
-        <v>/rʌn/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>v</v>
-      </c>
-      <c r="E4" t="str">
-        <v>t1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Hello</v>
-      </c>
-      <c r="B5" t="str">
-        <v>xin chào</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>t1</v>
-      </c>
-      <c r="F5">
-        <v>1773639230959</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>english</v>
-      </c>
-      <c r="B6" t="str">
-        <v>tiếng anh</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v>t1</v>
-      </c>
-      <c r="F6">
-        <v>1773640370257</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>